--- a/thread-strength/03_analyses/thread-summary.xlsx
+++ b/thread-strength/03_analyses/thread-summary.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mattg\Desktop\github\PSMFC-mytilus-byssus-pilot\thread-strength\02_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateofwa-my.sharepoint.com/personal/matthew_george_dfw_wa_gov/Documents/Desktop/Github/PSMFC-mytilus-byssus-pilot/thread-strength/03_analyses/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9023F421-1E01-4048-9215-63A3BC821F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{9023F421-1E01-4048-9215-63A3BC821F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75219F49-F9EC-424A-A9A5-609268A622F1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1468,7 +1481,7 @@
         <v>4.54</v>
       </c>
       <c r="L2" s="1">
-        <f>I2/K2*1000</f>
+        <f t="shared" ref="L2:L65" si="0">I2/K2*1000</f>
         <v>40.748898678414093</v>
       </c>
       <c r="M2" s="1" t="s">
@@ -1513,7 +1526,7 @@
         <v>3.05</v>
       </c>
       <c r="L3" s="1">
-        <f>I3/K3*1000</f>
+        <f t="shared" si="0"/>
         <v>29.508196721311478</v>
       </c>
       <c r="M3" s="1" t="s">
@@ -1558,7 +1571,7 @@
         <v>2.3199999999999998</v>
       </c>
       <c r="L4" s="1">
-        <f>I4/K4*1000</f>
+        <f t="shared" si="0"/>
         <v>68.965517241379317</v>
       </c>
       <c r="M4" s="1" t="s">
@@ -1603,7 +1616,7 @@
         <v>4.83</v>
       </c>
       <c r="L5" s="1">
-        <f>I5/K5*1000</f>
+        <f t="shared" si="0"/>
         <v>75.569358178053818</v>
       </c>
       <c r="M5" s="1" t="s">
@@ -1648,7 +1661,7 @@
         <v>5.94</v>
       </c>
       <c r="L6" s="1">
-        <f>I6/K6*1000</f>
+        <f t="shared" si="0"/>
         <v>57.239057239057239</v>
       </c>
       <c r="M6" s="1" t="s">
@@ -1693,7 +1706,7 @@
         <v>5.13</v>
       </c>
       <c r="L7" s="1">
-        <f>I7/K7*1000</f>
+        <f t="shared" si="0"/>
         <v>64.327485380116968</v>
       </c>
       <c r="M7" s="1" t="s">
@@ -1738,7 +1751,7 @@
         <v>2.98</v>
       </c>
       <c r="L8" s="1">
-        <f>I8/K8*1000</f>
+        <f t="shared" si="0"/>
         <v>88.926174496644308</v>
       </c>
       <c r="M8" s="1" t="s">
@@ -1783,7 +1796,7 @@
         <v>2.66</v>
       </c>
       <c r="L9" s="1">
-        <f>I9/K9*1000</f>
+        <f t="shared" si="0"/>
         <v>129.69924812030072</v>
       </c>
       <c r="M9" s="1" t="s">
@@ -1828,7 +1841,7 @@
         <v>2.92</v>
       </c>
       <c r="L10" s="1">
-        <f>I10/K10*1000</f>
+        <f t="shared" si="0"/>
         <v>49.657534246575338</v>
       </c>
       <c r="M10" s="1" t="s">
@@ -1873,7 +1886,7 @@
         <v>2.56</v>
       </c>
       <c r="L11" s="1">
-        <f>I11/K11*1000</f>
+        <f t="shared" si="0"/>
         <v>132.8125</v>
       </c>
       <c r="M11" s="1" t="s">
@@ -1918,7 +1931,7 @@
         <v>2.9</v>
       </c>
       <c r="L12" s="1">
-        <f>I12/K12*1000</f>
+        <f t="shared" si="0"/>
         <v>62.068965517241381</v>
       </c>
       <c r="M12" s="1" t="s">
@@ -1963,7 +1976,7 @@
         <v>2.5</v>
       </c>
       <c r="L13" s="1">
-        <f>I13/K13*1000</f>
+        <f t="shared" si="0"/>
         <v>102.00000000000001</v>
       </c>
       <c r="M13" s="1" t="s">
@@ -2008,7 +2021,7 @@
         <v>2.41</v>
       </c>
       <c r="L14" s="1">
-        <f>I14/K14*1000</f>
+        <f t="shared" si="0"/>
         <v>99.585062240663888</v>
       </c>
       <c r="M14" s="1" t="s">
@@ -2053,7 +2066,7 @@
         <v>2.34</v>
       </c>
       <c r="L15" s="1">
-        <f>I15/K15*1000</f>
+        <f t="shared" si="0"/>
         <v>104.70085470085471</v>
       </c>
       <c r="M15" s="1" t="s">
@@ -2098,7 +2111,7 @@
         <v>2.8</v>
       </c>
       <c r="L16" s="1">
-        <f>I16/K16*1000</f>
+        <f t="shared" si="0"/>
         <v>128.57142857142858</v>
       </c>
       <c r="M16" s="1" t="s">
@@ -2143,7 +2156,7 @@
         <v>3.33</v>
       </c>
       <c r="L17" s="1">
-        <f>I17/K17*1000</f>
+        <f t="shared" si="0"/>
         <v>112.61261261261261</v>
       </c>
       <c r="M17" s="1" t="s">
@@ -2188,7 +2201,7 @@
         <v>2.95</v>
       </c>
       <c r="L18" s="1">
-        <f>I18/K18*1000</f>
+        <f t="shared" si="0"/>
         <v>88.135593220338976</v>
       </c>
       <c r="M18" s="1" t="s">
@@ -2233,7 +2246,7 @@
         <v>2.1800000000000002</v>
       </c>
       <c r="L19" s="1">
-        <f>I19/K19*1000</f>
+        <f t="shared" si="0"/>
         <v>128.44036697247708</v>
       </c>
       <c r="M19" s="1" t="s">
@@ -2278,7 +2291,7 @@
         <v>2.4</v>
       </c>
       <c r="L20" s="1">
-        <f>I20/K20*1000</f>
+        <f t="shared" si="0"/>
         <v>10.416666666666668</v>
       </c>
       <c r="M20" s="1" t="s">
@@ -2323,7 +2336,7 @@
         <v>2.15</v>
       </c>
       <c r="L21" s="1">
-        <f>I21/K21*1000</f>
+        <f t="shared" si="0"/>
         <v>55.813953488372093</v>
       </c>
       <c r="M21" s="1" t="s">
@@ -2368,7 +2381,7 @@
         <v>3.9</v>
       </c>
       <c r="L22" s="1">
-        <f>I22/K22*1000</f>
+        <f t="shared" si="0"/>
         <v>97.435897435897431</v>
       </c>
       <c r="M22" s="1" t="s">
@@ -2413,7 +2426,7 @@
         <v>1.96</v>
       </c>
       <c r="L23" s="1">
-        <f>I23/K23*1000</f>
+        <f t="shared" si="0"/>
         <v>66.326530612244909</v>
       </c>
       <c r="M23" s="1" t="s">
@@ -2458,7 +2471,7 @@
         <v>2.3199999999999998</v>
       </c>
       <c r="L24" s="1">
-        <f>I24/K24*1000</f>
+        <f t="shared" si="0"/>
         <v>107.75862068965517</v>
       </c>
       <c r="M24" s="1" t="s">
@@ -2503,7 +2516,7 @@
         <v>2.68</v>
       </c>
       <c r="L25" s="1">
-        <f>I25/K25*1000</f>
+        <f t="shared" si="0"/>
         <v>29.850746268656717</v>
       </c>
       <c r="M25" s="1" t="s">
@@ -2548,7 +2561,7 @@
         <v>2.37</v>
       </c>
       <c r="L26" s="1">
-        <f>I26/K26*1000</f>
+        <f t="shared" si="0"/>
         <v>35.864978902953588</v>
       </c>
       <c r="M26" s="1" t="s">
@@ -2593,7 +2606,7 @@
         <v>2.4700000000000002</v>
       </c>
       <c r="L27" s="1">
-        <f>I27/K27*1000</f>
+        <f t="shared" si="0"/>
         <v>46.558704453441294</v>
       </c>
       <c r="M27" s="1" t="s">
@@ -2638,7 +2651,7 @@
         <v>2.66</v>
       </c>
       <c r="L28" s="1">
-        <f>I28/K28*1000</f>
+        <f t="shared" si="0"/>
         <v>78.94736842105263</v>
       </c>
       <c r="M28" s="1" t="s">
@@ -2683,7 +2696,7 @@
         <v>2.2400000000000002</v>
       </c>
       <c r="L29" s="1">
-        <f>I29/K29*1000</f>
+        <f t="shared" si="0"/>
         <v>198.66071428571428</v>
       </c>
       <c r="M29" s="1" t="s">
@@ -2728,7 +2741,7 @@
         <v>3.24</v>
       </c>
       <c r="L30" s="1">
-        <f>I30/K30*1000</f>
+        <f t="shared" si="0"/>
         <v>78.703703703703709</v>
       </c>
       <c r="M30" s="1" t="s">
@@ -2773,7 +2786,7 @@
         <v>3.26</v>
       </c>
       <c r="L31" s="1">
-        <f>I31/K31*1000</f>
+        <f t="shared" si="0"/>
         <v>79.75460122699387</v>
       </c>
       <c r="M31" s="1" t="s">
@@ -2818,7 +2831,7 @@
         <v>4.68</v>
       </c>
       <c r="L32" s="1">
-        <f>I32/K32*1000</f>
+        <f t="shared" si="0"/>
         <v>53.418803418803421</v>
       </c>
       <c r="M32" s="1" t="s">
@@ -2863,7 +2876,7 @@
         <v>3.17</v>
       </c>
       <c r="L33" s="1">
-        <f>I33/K33*1000</f>
+        <f t="shared" si="0"/>
         <v>42.586750788643542</v>
       </c>
       <c r="M33" s="1" t="s">
@@ -2908,7 +2921,7 @@
         <v>2.76</v>
       </c>
       <c r="L34" s="1">
-        <f>I34/K34*1000</f>
+        <f t="shared" si="0"/>
         <v>74.275362318840578</v>
       </c>
       <c r="M34" s="1" t="s">
@@ -2953,7 +2966,7 @@
         <v>1.95</v>
       </c>
       <c r="L35" s="1">
-        <f>I35/K35*1000</f>
+        <f t="shared" si="0"/>
         <v>110.25641025641025</v>
       </c>
       <c r="M35" s="1" t="s">
@@ -2998,7 +3011,7 @@
         <v>3.81</v>
       </c>
       <c r="L36" s="1">
-        <f>I36/K36*1000</f>
+        <f t="shared" si="0"/>
         <v>86.614173228346459</v>
       </c>
       <c r="M36" s="1" t="s">
@@ -3043,7 +3056,7 @@
         <v>4.18</v>
       </c>
       <c r="L37" s="1">
-        <f>I37/K37*1000</f>
+        <f t="shared" si="0"/>
         <v>78.947368421052644</v>
       </c>
       <c r="M37" s="1" t="s">
@@ -3088,7 +3101,7 @@
         <v>4.18</v>
       </c>
       <c r="L38" s="1">
-        <f>I38/K38*1000</f>
+        <f t="shared" si="0"/>
         <v>62.200956937799049</v>
       </c>
       <c r="M38" s="1" t="s">
@@ -3133,7 +3146,7 @@
         <v>2.68</v>
       </c>
       <c r="L39" s="1">
-        <f>I39/K39*1000</f>
+        <f t="shared" si="0"/>
         <v>80.223880597014926</v>
       </c>
       <c r="M39" s="1" t="s">
@@ -3178,7 +3191,7 @@
         <v>2.2599999999999998</v>
       </c>
       <c r="L40" s="1">
-        <f>I40/K40*1000</f>
+        <f t="shared" si="0"/>
         <v>88.495575221238951</v>
       </c>
       <c r="M40" s="1" t="s">
@@ -3223,7 +3236,7 @@
         <v>3.84</v>
       </c>
       <c r="L41" s="1">
-        <f>I41/K41*1000</f>
+        <f t="shared" si="0"/>
         <v>67.708333333333343</v>
       </c>
       <c r="M41" s="1" t="s">
@@ -3268,7 +3281,7 @@
         <v>2.14</v>
       </c>
       <c r="L42" s="1">
-        <f>I42/K42*1000</f>
+        <f t="shared" si="0"/>
         <v>81.775700934579433</v>
       </c>
       <c r="M42" s="1" t="s">
@@ -3313,7 +3326,7 @@
         <v>3.65</v>
       </c>
       <c r="L43" s="1">
-        <f>I43/K43*1000</f>
+        <f t="shared" si="0"/>
         <v>116.43835616438355</v>
       </c>
       <c r="M43" s="1" t="s">
@@ -3358,7 +3371,7 @@
         <v>3.71</v>
       </c>
       <c r="L44" s="1">
-        <f>I44/K44*1000</f>
+        <f t="shared" si="0"/>
         <v>102.42587601078168</v>
       </c>
       <c r="M44" s="1" t="s">
@@ -3403,7 +3416,7 @@
         <v>5.4</v>
       </c>
       <c r="L45" s="1">
-        <f>I45/K45*1000</f>
+        <f t="shared" si="0"/>
         <v>63.888888888888886</v>
       </c>
       <c r="M45" s="1" t="s">
@@ -3448,7 +3461,7 @@
         <v>4.63</v>
       </c>
       <c r="L46" s="1">
-        <f>I46/K46*1000</f>
+        <f t="shared" si="0"/>
         <v>52.915766738660906</v>
       </c>
       <c r="M46" s="1" t="s">
@@ -3493,7 +3506,7 @@
         <v>5.0199999999999996</v>
       </c>
       <c r="L47" s="1">
-        <f>I47/K47*1000</f>
+        <f t="shared" si="0"/>
         <v>74.701195219123505</v>
       </c>
       <c r="M47" s="1" t="s">
@@ -3538,7 +3551,7 @@
         <v>4.58</v>
       </c>
       <c r="L48" s="1">
-        <f>I48/K48*1000</f>
+        <f t="shared" si="0"/>
         <v>86.244541484716166</v>
       </c>
       <c r="M48" s="1" t="s">
@@ -3583,7 +3596,7 @@
         <v>2.63</v>
       </c>
       <c r="L49" s="1">
-        <f>I49/K49*1000</f>
+        <f t="shared" si="0"/>
         <v>76.04562737642587</v>
       </c>
       <c r="M49" s="1" t="s">
@@ -3628,7 +3641,7 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="L50" s="1">
-        <f>I50/K50*1000</f>
+        <f t="shared" si="0"/>
         <v>47.959183673469383</v>
       </c>
       <c r="M50" s="1" t="s">
@@ -3673,7 +3686,7 @@
         <v>3.48</v>
       </c>
       <c r="L51" s="1">
-        <f>I51/K51*1000</f>
+        <f t="shared" si="0"/>
         <v>24.425287356321842</v>
       </c>
       <c r="M51" s="1" t="s">
@@ -3718,7 +3731,7 @@
         <v>4.03</v>
       </c>
       <c r="L52" s="1">
-        <f>I52/K52*1000</f>
+        <f t="shared" si="0"/>
         <v>32.258064516129032</v>
       </c>
       <c r="M52" s="1" t="s">
@@ -3763,7 +3776,7 @@
         <v>5.39</v>
       </c>
       <c r="L53" s="1">
-        <f>I53/K53*1000</f>
+        <f t="shared" si="0"/>
         <v>51.020408163265316</v>
       </c>
       <c r="M53" s="1" t="s">
@@ -3808,7 +3821,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="L54" s="1">
-        <f>I54/K54*1000</f>
+        <f t="shared" si="0"/>
         <v>34.090909090909086</v>
       </c>
       <c r="M54" s="1" t="s">
@@ -3853,7 +3866,7 @@
         <v>3.98</v>
       </c>
       <c r="L55" s="1">
-        <f>I55/K55*1000</f>
+        <f t="shared" si="0"/>
         <v>54.020100502512562</v>
       </c>
       <c r="M55" s="1" t="s">
@@ -3898,7 +3911,7 @@
         <v>4.7300000000000004</v>
       </c>
       <c r="L56" s="1">
-        <f>I56/K56*1000</f>
+        <f t="shared" si="0"/>
         <v>98.308668076109939</v>
       </c>
       <c r="M56" s="1" t="s">
@@ -3943,7 +3956,7 @@
         <v>3.22</v>
       </c>
       <c r="L57" s="1">
-        <f>I57/K57*1000</f>
+        <f t="shared" si="0"/>
         <v>35.714285714285715</v>
       </c>
       <c r="M57" s="1" t="s">
@@ -3988,7 +4001,7 @@
         <v>3.37</v>
       </c>
       <c r="L58" s="1">
-        <f>I58/K58*1000</f>
+        <f t="shared" si="0"/>
         <v>56.379821958456972</v>
       </c>
       <c r="M58" s="1" t="s">
@@ -4033,7 +4046,7 @@
         <v>4.4400000000000004</v>
       </c>
       <c r="L59" s="1">
-        <f>I59/K59*1000</f>
+        <f t="shared" si="0"/>
         <v>51.801801801801801</v>
       </c>
       <c r="M59" s="1" t="s">
@@ -4078,7 +4091,7 @@
         <v>2.57</v>
       </c>
       <c r="L60" s="1">
-        <f>I60/K60*1000</f>
+        <f t="shared" si="0"/>
         <v>97.276264591439684</v>
       </c>
       <c r="M60" s="1" t="s">
@@ -4123,7 +4136,7 @@
         <v>1.58</v>
       </c>
       <c r="L61" s="1">
-        <f>I61/K61*1000</f>
+        <f t="shared" si="0"/>
         <v>180.37974683544303</v>
       </c>
       <c r="M61" s="1" t="s">
@@ -4168,7 +4181,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="L62" s="1">
-        <f>I62/K62*1000</f>
+        <f t="shared" si="0"/>
         <v>73.913043478260889</v>
       </c>
       <c r="N62" s="1" t="s">
@@ -4210,7 +4223,7 @@
         <v>4.17</v>
       </c>
       <c r="L63" s="1">
-        <f>I63/K63*1000</f>
+        <f t="shared" si="0"/>
         <v>37.170263788968825</v>
       </c>
       <c r="M63" s="1" t="s">
@@ -4255,7 +4268,7 @@
         <v>5.76</v>
       </c>
       <c r="L64" s="1">
-        <f>I64/K64*1000</f>
+        <f t="shared" si="0"/>
         <v>46.00694444444445</v>
       </c>
       <c r="M64" s="1" t="s">
@@ -4300,7 +4313,7 @@
         <v>5.12</v>
       </c>
       <c r="L65" s="1">
-        <f>I65/K65*1000</f>
+        <f t="shared" si="0"/>
         <v>66.40625</v>
       </c>
       <c r="M65" s="1" t="s">
@@ -4345,7 +4358,7 @@
         <v>3.3</v>
       </c>
       <c r="L66" s="1">
-        <f>I66/K66*1000</f>
+        <f t="shared" ref="L66:L129" si="1">I66/K66*1000</f>
         <v>28.787878787878789</v>
       </c>
       <c r="M66" s="1" t="s">
@@ -4390,7 +4403,7 @@
         <v>3.66</v>
       </c>
       <c r="L67" s="1">
-        <f>I67/K67*1000</f>
+        <f t="shared" si="1"/>
         <v>65.573770491803273</v>
       </c>
       <c r="M67" s="1" t="s">
@@ -4435,7 +4448,7 @@
         <v>3.71</v>
       </c>
       <c r="L68" s="1">
-        <f>I68/K68*1000</f>
+        <f t="shared" si="1"/>
         <v>67.385444743935309</v>
       </c>
       <c r="M68" s="1" t="s">
@@ -4480,7 +4493,7 @@
         <v>3.1</v>
       </c>
       <c r="L69" s="1">
-        <f>I69/K69*1000</f>
+        <f t="shared" si="1"/>
         <v>53.225806451612904</v>
       </c>
       <c r="M69" s="1" t="s">
@@ -4525,7 +4538,7 @@
         <v>4.07</v>
       </c>
       <c r="L70" s="1">
-        <f>I70/K70*1000</f>
+        <f t="shared" si="1"/>
         <v>27.027027027027025</v>
       </c>
       <c r="M70" s="1" t="s">
@@ -4570,7 +4583,7 @@
         <v>2.66</v>
       </c>
       <c r="L71" s="1">
-        <f>I71/K71*1000</f>
+        <f t="shared" si="1"/>
         <v>16.917293233082706</v>
       </c>
       <c r="M71" s="1" t="s">
@@ -4615,7 +4628,7 @@
         <v>2.89</v>
       </c>
       <c r="L72" s="1">
-        <f>I72/K72*1000</f>
+        <f t="shared" si="1"/>
         <v>62.283737024221452</v>
       </c>
       <c r="M72" s="1" t="s">
@@ -4660,7 +4673,7 @@
         <v>4.49</v>
       </c>
       <c r="L73" s="1">
-        <f>I73/K73*1000</f>
+        <f t="shared" si="1"/>
         <v>52.338530066815139</v>
       </c>
       <c r="M73" s="1" t="s">
@@ -4705,7 +4718,7 @@
         <v>2.11</v>
       </c>
       <c r="L74" s="1">
-        <f>I74/K74*1000</f>
+        <f t="shared" si="1"/>
         <v>37.914691943127963</v>
       </c>
       <c r="M74" s="1" t="s">
@@ -4750,7 +4763,7 @@
         <v>2.6</v>
       </c>
       <c r="L75" s="1">
-        <f>I75/K75*1000</f>
+        <f t="shared" si="1"/>
         <v>23.076923076923073</v>
       </c>
       <c r="M75" s="1" t="s">
@@ -4795,7 +4808,7 @@
         <v>2.67</v>
       </c>
       <c r="L76" s="1">
-        <f>I76/K76*1000</f>
+        <f t="shared" si="1"/>
         <v>58.052434456928843</v>
       </c>
       <c r="M76" s="1" t="s">
@@ -4840,7 +4853,7 @@
         <v>3.79</v>
       </c>
       <c r="L77" s="1">
-        <f>I77/K77*1000</f>
+        <f t="shared" si="1"/>
         <v>88.390501319261219</v>
       </c>
       <c r="M77" s="1" t="s">
@@ -4885,7 +4898,7 @@
         <v>5.36</v>
       </c>
       <c r="L78" s="1">
-        <f>I78/K78*1000</f>
+        <f t="shared" si="1"/>
         <v>34.514925373134325</v>
       </c>
       <c r="M78" s="1" t="s">
@@ -4930,7 +4943,7 @@
         <v>2.4900000000000002</v>
       </c>
       <c r="L79" s="1">
-        <f>I79/K79*1000</f>
+        <f t="shared" si="1"/>
         <v>110.44176706827309</v>
       </c>
       <c r="M79" s="1" t="s">
@@ -4975,7 +4988,7 @@
         <v>2.91</v>
       </c>
       <c r="L80" s="1">
-        <f>I80/K80*1000</f>
+        <f t="shared" si="1"/>
         <v>73.883161512027499</v>
       </c>
       <c r="M80" s="1" t="s">
@@ -5020,7 +5033,7 @@
         <v>3.14</v>
       </c>
       <c r="L81" s="1">
-        <f>I81/K81*1000</f>
+        <f t="shared" si="1"/>
         <v>60.509554140127392</v>
       </c>
       <c r="M81" s="1" t="s">
@@ -5065,7 +5078,7 @@
         <v>1.76</v>
       </c>
       <c r="L82" s="1">
-        <f>I82/K82*1000</f>
+        <f t="shared" si="1"/>
         <v>65.340909090909093</v>
       </c>
       <c r="M82" s="1" t="s">
@@ -5110,7 +5123,7 @@
         <v>2.5299999999999998</v>
       </c>
       <c r="L83" s="1">
-        <f>I83/K83*1000</f>
+        <f t="shared" si="1"/>
         <v>98.814229249011873</v>
       </c>
       <c r="M83" s="1" t="s">
@@ -5155,7 +5168,7 @@
         <v>1.72</v>
       </c>
       <c r="L84" s="1">
-        <f>I84/K84*1000</f>
+        <f t="shared" si="1"/>
         <v>133.72093023255815</v>
       </c>
       <c r="M84" s="1" t="s">
@@ -5200,7 +5213,7 @@
         <v>3.38</v>
       </c>
       <c r="L85" s="1">
-        <f>I85/K85*1000</f>
+        <f t="shared" si="1"/>
         <v>133.13609467455623</v>
       </c>
       <c r="M85" s="1" t="s">
@@ -5245,7 +5258,7 @@
         <v>3.39</v>
       </c>
       <c r="L86" s="1">
-        <f>I86/K86*1000</f>
+        <f t="shared" si="1"/>
         <v>120.94395280235986</v>
       </c>
       <c r="M86" s="1" t="s">
@@ -5290,7 +5303,7 @@
         <v>5.99</v>
       </c>
       <c r="L87" s="1">
-        <f>I87/K87*1000</f>
+        <f t="shared" si="1"/>
         <v>50.083472454090142</v>
       </c>
       <c r="M87" s="1" t="s">
@@ -5335,7 +5348,7 @@
         <v>2.76</v>
       </c>
       <c r="L88" s="1">
-        <f>I88/K88*1000</f>
+        <f t="shared" si="1"/>
         <v>86.956521739130437</v>
       </c>
       <c r="M88" s="1" t="s">
@@ -5380,7 +5393,7 @@
         <v>3.62</v>
       </c>
       <c r="L89" s="1">
-        <f>I89/K89*1000</f>
+        <f t="shared" si="1"/>
         <v>81.491712707182316</v>
       </c>
       <c r="M89" s="1" t="s">
@@ -5425,7 +5438,7 @@
         <v>2.95</v>
       </c>
       <c r="L90" s="1">
-        <f>I90/K90*1000</f>
+        <f t="shared" si="1"/>
         <v>110.16949152542372</v>
       </c>
       <c r="M90" s="1" t="s">
@@ -5470,7 +5483,7 @@
         <v>2</v>
       </c>
       <c r="L91" s="1">
-        <f>I91/K91*1000</f>
+        <f t="shared" si="1"/>
         <v>85</v>
       </c>
       <c r="M91" s="1" t="s">
@@ -5515,7 +5528,7 @@
         <v>1.73</v>
       </c>
       <c r="L92" s="1">
-        <f>I92/K92*1000</f>
+        <f t="shared" si="1"/>
         <v>106.93641618497109</v>
       </c>
       <c r="M92" s="1" t="s">
@@ -5560,7 +5573,7 @@
         <v>1.63</v>
       </c>
       <c r="L93" s="1">
-        <f>I93/K93*1000</f>
+        <f t="shared" si="1"/>
         <v>101.22699386503069</v>
       </c>
       <c r="M93" s="1" t="s">
@@ -5605,7 +5618,7 @@
         <v>4.5199999999999996</v>
       </c>
       <c r="L94" s="1">
-        <f>I94/K94*1000</f>
+        <f t="shared" si="1"/>
         <v>74.115044247787623</v>
       </c>
       <c r="M94" s="1" t="s">
@@ -5650,7 +5663,7 @@
         <v>4.67</v>
       </c>
       <c r="L95" s="1">
-        <f>I95/K95*1000</f>
+        <f t="shared" si="1"/>
         <v>48.179871520342616</v>
       </c>
       <c r="M95" s="1" t="s">
@@ -5695,7 +5708,7 @@
         <v>4.83</v>
       </c>
       <c r="L96" s="1">
-        <f>I96/K96*1000</f>
+        <f t="shared" si="1"/>
         <v>62.111801242236027</v>
       </c>
       <c r="M96" s="1" t="s">
@@ -5740,7 +5753,7 @@
         <v>2.88</v>
       </c>
       <c r="L97" s="1">
-        <f>I97/K97*1000</f>
+        <f t="shared" si="1"/>
         <v>64.236111111111114</v>
       </c>
       <c r="M97" s="1" t="s">
@@ -5785,7 +5798,7 @@
         <v>3.56</v>
       </c>
       <c r="L98" s="1">
-        <f>I98/K98*1000</f>
+        <f t="shared" si="1"/>
         <v>68.82022471910112</v>
       </c>
       <c r="M98" s="1" t="s">
@@ -5830,7 +5843,7 @@
         <v>2.16</v>
       </c>
       <c r="L99" s="1">
-        <f>I99/K99*1000</f>
+        <f t="shared" si="1"/>
         <v>67.129629629629619</v>
       </c>
       <c r="M99" s="1" t="s">
@@ -5875,7 +5888,7 @@
         <v>4.54</v>
       </c>
       <c r="L100" s="1">
-        <f>I100/K100*1000</f>
+        <f t="shared" si="1"/>
         <v>112.33480176211454</v>
       </c>
       <c r="M100" s="1" t="s">
@@ -5920,7 +5933,7 @@
         <v>3.39</v>
       </c>
       <c r="L101" s="1">
-        <f>I101/K101*1000</f>
+        <f t="shared" si="1"/>
         <v>98.820058997050154</v>
       </c>
       <c r="M101" s="1" t="s">
@@ -5965,7 +5978,7 @@
         <v>3.36</v>
       </c>
       <c r="L102" s="1">
-        <f>I102/K102*1000</f>
+        <f t="shared" si="1"/>
         <v>61.011904761904759</v>
       </c>
       <c r="M102" s="1" t="s">
@@ -6010,7 +6023,7 @@
         <v>5.2</v>
       </c>
       <c r="L103" s="1">
-        <f>I103/K103*1000</f>
+        <f t="shared" si="1"/>
         <v>75</v>
       </c>
       <c r="M103" s="1" t="s">
@@ -6055,7 +6068,7 @@
         <v>4.3099999999999996</v>
       </c>
       <c r="L104" s="1">
-        <f>I104/K104*1000</f>
+        <f t="shared" si="1"/>
         <v>46.403712296983763</v>
       </c>
       <c r="M104" s="1" t="s">
@@ -6100,7 +6113,7 @@
         <v>3.48</v>
       </c>
       <c r="L105" s="1">
-        <f>I105/K105*1000</f>
+        <f t="shared" si="1"/>
         <v>21.551724137931032</v>
       </c>
       <c r="M105" s="1" t="s">
@@ -6145,7 +6158,7 @@
         <v>2.69</v>
       </c>
       <c r="L106" s="1">
-        <f>I106/K106*1000</f>
+        <f t="shared" si="1"/>
         <v>118.95910780669146</v>
       </c>
       <c r="M106" s="1" t="s">
@@ -6190,7 +6203,7 @@
         <v>3.11</v>
       </c>
       <c r="L107" s="1">
-        <f>I107/K107*1000</f>
+        <f t="shared" si="1"/>
         <v>70.739549839228303</v>
       </c>
       <c r="M107" s="1" t="s">
@@ -6235,7 +6248,7 @@
         <v>2.42</v>
       </c>
       <c r="L108" s="1">
-        <f>I108/K108*1000</f>
+        <f t="shared" si="1"/>
         <v>107.43801652892563</v>
       </c>
       <c r="M108" s="1" t="s">
@@ -6280,7 +6293,7 @@
         <v>3.55</v>
       </c>
       <c r="L109" s="1">
-        <f>I109/K109*1000</f>
+        <f t="shared" si="1"/>
         <v>40.845070422535215</v>
       </c>
       <c r="M109" s="1" t="s">
@@ -6325,7 +6338,7 @@
         <v>2.88</v>
       </c>
       <c r="L110" s="1">
-        <f>I110/K110*1000</f>
+        <f t="shared" si="1"/>
         <v>48.611111111111121</v>
       </c>
       <c r="M110" s="1" t="s">
@@ -6370,7 +6383,7 @@
         <v>2.91</v>
       </c>
       <c r="L111" s="1">
-        <f>I111/K111*1000</f>
+        <f t="shared" si="1"/>
         <v>24.054982817869416</v>
       </c>
       <c r="M111" s="1" t="s">
@@ -6415,7 +6428,7 @@
         <v>3.39</v>
       </c>
       <c r="L112" s="1">
-        <f>I112/K112*1000</f>
+        <f t="shared" si="1"/>
         <v>69.321533923303832</v>
       </c>
       <c r="M112" s="1" t="s">
@@ -6460,7 +6473,7 @@
         <v>2.5</v>
       </c>
       <c r="L113" s="1">
-        <f>I113/K113*1000</f>
+        <f t="shared" si="1"/>
         <v>74</v>
       </c>
       <c r="M113" s="1" t="s">
@@ -6505,7 +6518,7 @@
         <v>3.87</v>
       </c>
       <c r="L114" s="1">
-        <f>I114/K114*1000</f>
+        <f t="shared" si="1"/>
         <v>67.183462532299743</v>
       </c>
       <c r="M114" s="1" t="s">
@@ -6550,7 +6563,7 @@
         <v>2.58</v>
       </c>
       <c r="L115" s="1">
-        <f>I115/K115*1000</f>
+        <f t="shared" si="1"/>
         <v>71.705426356589143</v>
       </c>
       <c r="M115" s="1" t="s">
@@ -6595,7 +6608,7 @@
         <v>2.64</v>
       </c>
       <c r="L116" s="1">
-        <f>I116/K116*1000</f>
+        <f t="shared" si="1"/>
         <v>64.393939393939391</v>
       </c>
       <c r="M116" s="1" t="s">
@@ -6640,7 +6653,7 @@
         <v>2.39</v>
       </c>
       <c r="L117" s="1">
-        <f>I117/K117*1000</f>
+        <f t="shared" si="1"/>
         <v>173.64016736401672</v>
       </c>
       <c r="M117" s="1" t="s">
@@ -6685,7 +6698,7 @@
         <v>2.76</v>
       </c>
       <c r="L118" s="1">
-        <f>I118/K118*1000</f>
+        <f t="shared" si="1"/>
         <v>161.23188405797103</v>
       </c>
       <c r="M118" s="1" t="s">
@@ -6730,7 +6743,7 @@
         <v>3.8</v>
       </c>
       <c r="L119" s="1">
-        <f>I119/K119*1000</f>
+        <f t="shared" si="1"/>
         <v>71.052631578947384</v>
       </c>
       <c r="M119" s="1" t="s">
@@ -6775,7 +6788,7 @@
         <v>3.5</v>
       </c>
       <c r="L120" s="1">
-        <f>I120/K120*1000</f>
+        <f t="shared" si="1"/>
         <v>141.42857142857144</v>
       </c>
       <c r="M120" s="1" t="s">
@@ -6820,7 +6833,7 @@
         <v>5.62</v>
       </c>
       <c r="L121" s="1">
-        <f>I121/K121*1000</f>
+        <f t="shared" si="1"/>
         <v>76.512455516014242</v>
       </c>
       <c r="M121" s="1" t="s">
@@ -6865,7 +6878,7 @@
         <v>3.38</v>
       </c>
       <c r="L122" s="1">
-        <f>I122/K122*1000</f>
+        <f t="shared" si="1"/>
         <v>45.857988165680474</v>
       </c>
       <c r="M122" s="1" t="s">
@@ -6910,7 +6923,7 @@
         <v>2.81</v>
       </c>
       <c r="L123" s="1">
-        <f>I123/K123*1000</f>
+        <f t="shared" si="1"/>
         <v>97.864768683274022</v>
       </c>
       <c r="M123" s="1" t="s">
@@ -6955,7 +6968,7 @@
         <v>5.18</v>
       </c>
       <c r="L124" s="1">
-        <f>I124/K124*1000</f>
+        <f t="shared" si="1"/>
         <v>62.74131274131274</v>
       </c>
       <c r="M124" s="1" t="s">
@@ -7000,7 +7013,7 @@
         <v>4.26</v>
       </c>
       <c r="L125" s="1">
-        <f>I125/K125*1000</f>
+        <f t="shared" si="1"/>
         <v>58.685446009389672</v>
       </c>
       <c r="M125" s="1" t="s">
@@ -7045,7 +7058,7 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="L126" s="1">
-        <f>I126/K126*1000</f>
+        <f t="shared" si="1"/>
         <v>71.428571428571431</v>
       </c>
       <c r="M126" s="1" t="s">
@@ -7090,7 +7103,7 @@
         <v>4.13</v>
       </c>
       <c r="L127" s="1">
-        <f>I127/K127*1000</f>
+        <f t="shared" si="1"/>
         <v>59.322033898305087</v>
       </c>
       <c r="M127" s="1" t="s">
@@ -7135,7 +7148,7 @@
         <v>4.8499999999999996</v>
       </c>
       <c r="L128" s="1">
-        <f>I128/K128*1000</f>
+        <f t="shared" si="1"/>
         <v>75.257731958762903</v>
       </c>
       <c r="M128" s="1" t="s">
@@ -7180,7 +7193,7 @@
         <v>5.05</v>
       </c>
       <c r="L129" s="1">
-        <f>I129/K129*1000</f>
+        <f t="shared" si="1"/>
         <v>50.495049504950501</v>
       </c>
       <c r="M129" s="1" t="s">
@@ -7225,7 +7238,7 @@
         <v>4.47</v>
       </c>
       <c r="L130" s="1">
-        <f>I130/K130*1000</f>
+        <f t="shared" ref="L130:L193" si="2">I130/K130*1000</f>
         <v>67.114093959731548</v>
       </c>
       <c r="M130" s="1" t="s">
@@ -7270,7 +7283,7 @@
         <v>3.85</v>
       </c>
       <c r="L131" s="1">
-        <f>I131/K131*1000</f>
+        <f t="shared" si="2"/>
         <v>61.038961038961034</v>
       </c>
       <c r="M131" s="1" t="s">
@@ -7315,7 +7328,7 @@
         <v>3.73</v>
       </c>
       <c r="L132" s="1">
-        <f>I132/K132*1000</f>
+        <f t="shared" si="2"/>
         <v>63.002680965147455</v>
       </c>
       <c r="M132" s="1" t="s">
@@ -7360,7 +7373,7 @@
         <v>4.05</v>
       </c>
       <c r="L133" s="1">
-        <f>I133/K133*1000</f>
+        <f t="shared" si="2"/>
         <v>24.691358024691361</v>
       </c>
       <c r="M133" s="1" t="s">
@@ -7405,7 +7418,7 @@
         <v>5.96</v>
       </c>
       <c r="L134" s="1">
-        <f>I134/K134*1000</f>
+        <f t="shared" si="2"/>
         <v>100.67114093959731</v>
       </c>
       <c r="M134" s="1" t="s">
@@ -7450,7 +7463,7 @@
         <v>4.78</v>
       </c>
       <c r="L135" s="1">
-        <f>I135/K135*1000</f>
+        <f t="shared" si="2"/>
         <v>56.485355648535567</v>
       </c>
       <c r="M135" s="1" t="s">
@@ -7495,7 +7508,7 @@
         <v>2.5499999999999998</v>
       </c>
       <c r="L136" s="1">
-        <f>I136/K136*1000</f>
+        <f t="shared" si="2"/>
         <v>74.509803921568647</v>
       </c>
       <c r="M136" s="1" t="s">
@@ -7540,7 +7553,7 @@
         <v>2.4900000000000002</v>
       </c>
       <c r="L137" s="1">
-        <f>I137/K137*1000</f>
+        <f t="shared" si="2"/>
         <v>116.46586345381523</v>
       </c>
       <c r="M137" s="1" t="s">
@@ -7585,7 +7598,7 @@
         <v>2.71</v>
       </c>
       <c r="L138" s="1">
-        <f>I138/K138*1000</f>
+        <f t="shared" si="2"/>
         <v>51.660516605166059</v>
       </c>
       <c r="M138" s="1" t="s">
@@ -7630,7 +7643,7 @@
         <v>2.8</v>
       </c>
       <c r="L139" s="1">
-        <f>I139/K139*1000</f>
+        <f t="shared" si="2"/>
         <v>30.357142857142861</v>
       </c>
       <c r="M139" s="1" t="s">
@@ -7675,7 +7688,7 @@
         <v>4</v>
       </c>
       <c r="L140" s="1">
-        <f>I140/K140*1000</f>
+        <f t="shared" si="2"/>
         <v>66.25</v>
       </c>
       <c r="M140" s="1" t="s">
@@ -7720,7 +7733,7 @@
         <v>3.71</v>
       </c>
       <c r="L141" s="1">
-        <f>I141/K141*1000</f>
+        <f t="shared" si="2"/>
         <v>49.865229110512132</v>
       </c>
       <c r="M141" s="1" t="s">
@@ -7765,7 +7778,7 @@
         <v>2.76</v>
       </c>
       <c r="L142" s="1">
-        <f>I142/K142*1000</f>
+        <f t="shared" si="2"/>
         <v>52.536231884057969</v>
       </c>
       <c r="M142" s="1" t="s">
@@ -7810,7 +7823,7 @@
         <v>3.53</v>
       </c>
       <c r="L143" s="1">
-        <f>I143/K143*1000</f>
+        <f t="shared" si="2"/>
         <v>46.742209631728052</v>
       </c>
       <c r="M143" s="1" t="s">
@@ -7855,7 +7868,7 @@
         <v>2.98</v>
       </c>
       <c r="L144" s="1">
-        <f>I144/K144*1000</f>
+        <f t="shared" si="2"/>
         <v>41.946308724832214</v>
       </c>
       <c r="M144" s="1" t="s">
@@ -7900,7 +7913,7 @@
         <v>2.86</v>
       </c>
       <c r="L145" s="1">
-        <f>I145/K145*1000</f>
+        <f t="shared" si="2"/>
         <v>66.433566433566426</v>
       </c>
       <c r="M145" s="1" t="s">
@@ -7945,7 +7958,7 @@
         <v>4.12</v>
       </c>
       <c r="L146" s="1">
-        <f>I146/K146*1000</f>
+        <f t="shared" si="2"/>
         <v>89.805825242718441</v>
       </c>
       <c r="M146" s="1" t="s">
@@ -7990,7 +8003,7 @@
         <v>1.76</v>
       </c>
       <c r="L147" s="1">
-        <f>I147/K147*1000</f>
+        <f t="shared" si="2"/>
         <v>136.36363636363635</v>
       </c>
       <c r="M147" s="1" t="s">
@@ -8035,7 +8048,7 @@
         <v>4.37</v>
       </c>
       <c r="L148" s="1">
-        <f>I148/K148*1000</f>
+        <f t="shared" si="2"/>
         <v>59.496567505720826</v>
       </c>
       <c r="M148" s="1" t="s">
@@ -8080,7 +8093,7 @@
         <v>2.83</v>
       </c>
       <c r="L149" s="1">
-        <f>I149/K149*1000</f>
+        <f t="shared" si="2"/>
         <v>132.50883392226149</v>
       </c>
       <c r="M149" s="1" t="s">
@@ -8125,7 +8138,7 @@
         <v>2.4300000000000002</v>
       </c>
       <c r="L150" s="1">
-        <f>I150/K150*1000</f>
+        <f t="shared" si="2"/>
         <v>67.901234567901227</v>
       </c>
       <c r="M150" s="1" t="s">
@@ -8170,7 +8183,7 @@
         <v>2.58</v>
       </c>
       <c r="L151" s="1">
-        <f>I151/K151*1000</f>
+        <f t="shared" si="2"/>
         <v>63.953488372093027</v>
       </c>
       <c r="M151" s="1" t="s">
@@ -8215,7 +8228,7 @@
         <v>3.32</v>
       </c>
       <c r="L152" s="1">
-        <f>I152/K152*1000</f>
+        <f t="shared" si="2"/>
         <v>57.228915662650607</v>
       </c>
       <c r="M152" s="1" t="s">
@@ -8260,7 +8273,7 @@
         <v>3.94</v>
       </c>
       <c r="L153" s="1">
-        <f>I153/K153*1000</f>
+        <f t="shared" si="2"/>
         <v>39.340101522842637</v>
       </c>
       <c r="M153" s="1" t="s">
@@ -8305,7 +8318,7 @@
         <v>2.5099999999999998</v>
       </c>
       <c r="L154" s="1">
-        <f>I154/K154*1000</f>
+        <f t="shared" si="2"/>
         <v>33.864541832669325</v>
       </c>
       <c r="M154" s="1" t="s">
@@ -8350,7 +8363,7 @@
         <v>2.98</v>
       </c>
       <c r="L155" s="1">
-        <f>I155/K155*1000</f>
+        <f t="shared" si="2"/>
         <v>67.114093959731548</v>
       </c>
       <c r="M155" s="1" t="s">
@@ -8395,7 +8408,7 @@
         <v>2.3199999999999998</v>
       </c>
       <c r="L156" s="1">
-        <f>I156/K156*1000</f>
+        <f t="shared" si="2"/>
         <v>28.017241379310349</v>
       </c>
       <c r="M156" s="1" t="s">
@@ -8440,7 +8453,7 @@
         <v>4.54</v>
       </c>
       <c r="L157" s="1">
-        <f>I157/K157*1000</f>
+        <f t="shared" si="2"/>
         <v>53.964757709251096</v>
       </c>
       <c r="M157" s="1" t="s">
@@ -8485,7 +8498,7 @@
         <v>4.3899999999999997</v>
       </c>
       <c r="L158" s="1">
-        <f>I158/K158*1000</f>
+        <f t="shared" si="2"/>
         <v>37.58542141230069</v>
       </c>
       <c r="M158" s="1" t="s">
@@ -8530,7 +8543,7 @@
         <v>4.37</v>
       </c>
       <c r="L159" s="1">
-        <f>I159/K159*1000</f>
+        <f t="shared" si="2"/>
         <v>73.226544622425635</v>
       </c>
       <c r="M159" s="1" t="s">
@@ -8575,7 +8588,7 @@
         <v>3.44</v>
       </c>
       <c r="L160" s="1">
-        <f>I160/K160*1000</f>
+        <f t="shared" si="2"/>
         <v>78.488372093023258</v>
       </c>
       <c r="M160" s="1" t="s">
@@ -8620,7 +8633,7 @@
         <v>4.18</v>
       </c>
       <c r="L161" s="1">
-        <f>I161/K161*1000</f>
+        <f t="shared" si="2"/>
         <v>72.966507177033492</v>
       </c>
       <c r="M161" s="1" t="s">
@@ -8665,7 +8678,7 @@
         <v>6</v>
       </c>
       <c r="L162" s="1">
-        <f>I162/K162*1000</f>
+        <f t="shared" si="2"/>
         <v>62.5</v>
       </c>
       <c r="M162" s="1" t="s">
@@ -8710,7 +8723,7 @@
         <v>2.63</v>
       </c>
       <c r="L163" s="1">
-        <f>I163/K163*1000</f>
+        <f t="shared" si="2"/>
         <v>93.155893536121681</v>
       </c>
       <c r="M163" s="1" t="s">
@@ -8755,7 +8768,7 @@
         <v>1.99</v>
       </c>
       <c r="L164" s="1">
-        <f>I164/K164*1000</f>
+        <f t="shared" si="2"/>
         <v>92.964824120603012</v>
       </c>
       <c r="M164" s="1" t="s">
@@ -8800,7 +8813,7 @@
         <v>2.09</v>
       </c>
       <c r="L165" s="1">
-        <f>I165/K165*1000</f>
+        <f t="shared" si="2"/>
         <v>117.22488038277513</v>
       </c>
       <c r="M165" s="1" t="s">
@@ -8845,7 +8858,7 @@
         <v>2.98</v>
       </c>
       <c r="L166" s="1">
-        <f>I166/K166*1000</f>
+        <f t="shared" si="2"/>
         <v>65.436241610738264</v>
       </c>
       <c r="M166" s="1" t="s">
@@ -8890,7 +8903,7 @@
         <v>2.6</v>
       </c>
       <c r="L167" s="1">
-        <f>I167/K167*1000</f>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
       <c r="M167" s="1" t="s">
@@ -8935,7 +8948,7 @@
         <v>2.83</v>
       </c>
       <c r="L168" s="1">
-        <f>I168/K168*1000</f>
+        <f t="shared" si="2"/>
         <v>60.070671378091873</v>
       </c>
       <c r="M168" s="1" t="s">
@@ -8980,7 +8993,7 @@
         <v>3.11</v>
       </c>
       <c r="L169" s="1">
-        <f>I169/K169*1000</f>
+        <f t="shared" si="2"/>
         <v>69.131832797427663</v>
       </c>
       <c r="M169" s="1" t="s">
@@ -9025,7 +9038,7 @@
         <v>2.4300000000000002</v>
       </c>
       <c r="L170" s="1">
-        <f>I170/K170*1000</f>
+        <f t="shared" si="2"/>
         <v>96.707818930041142</v>
       </c>
       <c r="M170" s="1" t="s">
@@ -9070,7 +9083,7 @@
         <v>4.1100000000000003</v>
       </c>
       <c r="L171" s="1">
-        <f>I171/K171*1000</f>
+        <f t="shared" si="2"/>
         <v>121.654501216545</v>
       </c>
       <c r="M171" s="1" t="s">
@@ -9115,7 +9128,7 @@
         <v>2.68</v>
       </c>
       <c r="L172" s="1">
-        <f>I172/K172*1000</f>
+        <f t="shared" si="2"/>
         <v>72.761194029850742</v>
       </c>
       <c r="M172" s="1" t="s">
@@ -9160,7 +9173,7 @@
         <v>2.37</v>
       </c>
       <c r="L173" s="1">
-        <f>I173/K173*1000</f>
+        <f t="shared" si="2"/>
         <v>154.00843881856537</v>
       </c>
       <c r="M173" s="1" t="s">
@@ -9205,7 +9218,7 @@
         <v>1.78</v>
       </c>
       <c r="L174" s="1">
-        <f>I174/K174*1000</f>
+        <f t="shared" si="2"/>
         <v>61.797752808988761</v>
       </c>
       <c r="M174" s="1" t="s">
@@ -9250,7 +9263,7 @@
         <v>4.29</v>
       </c>
       <c r="L175" s="1">
-        <f>I175/K175*1000</f>
+        <f t="shared" si="2"/>
         <v>53.613053613053616</v>
       </c>
       <c r="M175" s="1" t="s">
@@ -9295,7 +9308,7 @@
         <v>2.93</v>
       </c>
       <c r="L176" s="1">
-        <f>I176/K176*1000</f>
+        <f t="shared" si="2"/>
         <v>51.194539249146757</v>
       </c>
       <c r="M176" s="1" t="s">
@@ -9340,7 +9353,7 @@
         <v>3.18</v>
       </c>
       <c r="L177" s="1">
-        <f>I177/K177*1000</f>
+        <f t="shared" si="2"/>
         <v>53.459119496855351</v>
       </c>
       <c r="M177" s="1" t="s">
@@ -9385,7 +9398,7 @@
         <v>2.88</v>
       </c>
       <c r="L178" s="1">
-        <f>I178/K178*1000</f>
+        <f t="shared" si="2"/>
         <v>72.916666666666671</v>
       </c>
       <c r="M178" s="1" t="s">
@@ -9430,7 +9443,7 @@
         <v>2.31</v>
       </c>
       <c r="L179" s="1">
-        <f>I179/K179*1000</f>
+        <f t="shared" si="2"/>
         <v>80.086580086580085</v>
       </c>
       <c r="M179" s="1" t="s">
@@ -9475,7 +9488,7 @@
         <v>1.97</v>
       </c>
       <c r="L180" s="1">
-        <f>I180/K180*1000</f>
+        <f t="shared" si="2"/>
         <v>124.36548223350253</v>
       </c>
       <c r="M180" s="1" t="s">
@@ -9520,7 +9533,7 @@
         <v>2.83</v>
       </c>
       <c r="L181" s="1">
-        <f>I181/K181*1000</f>
+        <f t="shared" si="2"/>
         <v>37.102473498233216</v>
       </c>
       <c r="M181" s="1" t="s">
@@ -9565,7 +9578,7 @@
         <v>1.07</v>
       </c>
       <c r="L182" s="1">
-        <f>I182/K182*1000</f>
+        <f t="shared" si="2"/>
         <v>144.85981308411215</v>
       </c>
       <c r="M182" s="1" t="s">
@@ -9610,7 +9623,7 @@
         <v>1.75</v>
       </c>
       <c r="L183" s="1">
-        <f>I183/K183*1000</f>
+        <f t="shared" si="2"/>
         <v>71.428571428571431</v>
       </c>
       <c r="M183" s="1" t="s">
@@ -9655,7 +9668,7 @@
         <v>1.19</v>
       </c>
       <c r="L184" s="1">
-        <f>I184/K184*1000</f>
+        <f t="shared" si="2"/>
         <v>147.05882352941177</v>
       </c>
       <c r="M184" s="1" t="s">
@@ -9700,7 +9713,7 @@
         <v>1.43</v>
       </c>
       <c r="L185" s="1">
-        <f>I185/K185*1000</f>
+        <f t="shared" si="2"/>
         <v>48.951048951048961</v>
       </c>
       <c r="M185" s="1" t="s">
@@ -9745,7 +9758,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="L186" s="1">
-        <f>I186/K186*1000</f>
+        <f t="shared" si="2"/>
         <v>57.017543859649123</v>
       </c>
       <c r="M186" s="1" t="s">
@@ -9790,7 +9803,7 @@
         <v>1.32</v>
       </c>
       <c r="L187" s="1">
-        <f>I187/K187*1000</f>
+        <f t="shared" si="2"/>
         <v>30.303030303030305</v>
       </c>
       <c r="M187" s="1" t="s">
@@ -9835,7 +9848,7 @@
         <v>1.75</v>
       </c>
       <c r="L188" s="1">
-        <f>I188/K188*1000</f>
+        <f t="shared" si="2"/>
         <v>99.999999999999986</v>
       </c>
       <c r="M188" s="1" t="s">
@@ -9880,7 +9893,7 @@
         <v>2.99</v>
       </c>
       <c r="L189" s="1">
-        <f>I189/K189*1000</f>
+        <f t="shared" si="2"/>
         <v>25.083612040133776</v>
       </c>
       <c r="M189" s="1" t="s">
@@ -9925,7 +9938,7 @@
         <v>1.48</v>
       </c>
       <c r="L190" s="1">
-        <f>I190/K190*1000</f>
+        <f t="shared" si="2"/>
         <v>60.810810810810807</v>
       </c>
       <c r="M190" s="1" t="s">
@@ -9970,7 +9983,7 @@
         <v>2.42</v>
       </c>
       <c r="L191" s="1">
-        <f>I191/K191*1000</f>
+        <f t="shared" si="2"/>
         <v>14.462809917355374</v>
       </c>
       <c r="M191" s="1" t="s">
@@ -10015,7 +10028,7 @@
         <v>3.03</v>
       </c>
       <c r="L192" s="1">
-        <f>I192/K192*1000</f>
+        <f t="shared" si="2"/>
         <v>66.006600660066013</v>
       </c>
       <c r="M192" s="1" t="s">
@@ -10060,7 +10073,7 @@
         <v>2.44</v>
       </c>
       <c r="L193" s="1">
-        <f>I193/K193*1000</f>
+        <f t="shared" si="2"/>
         <v>125</v>
       </c>
       <c r="M193" s="1" t="s">
@@ -10105,7 +10118,7 @@
         <v>2</v>
       </c>
       <c r="L194" s="1">
-        <f>I194/K194*1000</f>
+        <f t="shared" ref="L194:L257" si="3">I194/K194*1000</f>
         <v>100</v>
       </c>
       <c r="M194" s="1" t="s">
@@ -10150,7 +10163,7 @@
         <v>2.84</v>
       </c>
       <c r="L195" s="1">
-        <f>I195/K195*1000</f>
+        <f t="shared" si="3"/>
         <v>61.619718309859159</v>
       </c>
       <c r="M195" s="1" t="s">
@@ -10195,7 +10208,7 @@
         <v>2.42</v>
       </c>
       <c r="L196" s="1">
-        <f>I196/K196*1000</f>
+        <f t="shared" si="3"/>
         <v>59.917355371900818</v>
       </c>
       <c r="M196" s="1" t="s">
@@ -10240,7 +10253,7 @@
         <v>3.71</v>
       </c>
       <c r="L197" s="1">
-        <f>I197/K197*1000</f>
+        <f t="shared" si="3"/>
         <v>39.083557951482476</v>
       </c>
       <c r="M197" s="1" t="s">
@@ -10285,7 +10298,7 @@
         <v>3.21</v>
       </c>
       <c r="L198" s="1">
-        <f>I198/K198*1000</f>
+        <f t="shared" si="3"/>
         <v>37.383177570093459</v>
       </c>
       <c r="M198" s="1" t="s">
@@ -10330,7 +10343,7 @@
         <v>1.91</v>
       </c>
       <c r="L199" s="1">
-        <f>I199/K199*1000</f>
+        <f t="shared" si="3"/>
         <v>65.445026178010465</v>
       </c>
       <c r="M199" s="1" t="s">
@@ -10375,7 +10388,7 @@
         <v>2.31</v>
       </c>
       <c r="L200" s="1">
-        <f>I200/K200*1000</f>
+        <f t="shared" si="3"/>
         <v>36.796536796536799</v>
       </c>
       <c r="M200" s="1" t="s">
@@ -10420,7 +10433,7 @@
         <v>2</v>
       </c>
       <c r="L201" s="1">
-        <f>I201/K201*1000</f>
+        <f t="shared" si="3"/>
         <v>77.5</v>
       </c>
       <c r="M201" s="1" t="s">
@@ -10465,7 +10478,7 @@
         <v>4.09</v>
       </c>
       <c r="L202" s="1">
-        <f>I202/K202*1000</f>
+        <f t="shared" si="3"/>
         <v>31.78484107579462</v>
       </c>
       <c r="M202" s="1" t="s">
@@ -10510,7 +10523,7 @@
         <v>1.56</v>
       </c>
       <c r="L203" s="1">
-        <f>I203/K203*1000</f>
+        <f t="shared" si="3"/>
         <v>86.538461538461533</v>
       </c>
       <c r="M203" s="1" t="s">
@@ -10555,7 +10568,7 @@
         <v>1.06</v>
       </c>
       <c r="L204" s="1">
-        <f>I204/K204*1000</f>
+        <f t="shared" si="3"/>
         <v>150.94339622641508</v>
       </c>
       <c r="M204" s="1" t="s">
@@ -10600,7 +10613,7 @@
         <v>1.02</v>
       </c>
       <c r="L205" s="1">
-        <f>I205/K205*1000</f>
+        <f t="shared" si="3"/>
         <v>132.35294117647058</v>
       </c>
       <c r="M205" s="1" t="s">
@@ -10645,7 +10658,7 @@
         <v>1.47</v>
       </c>
       <c r="L206" s="1">
-        <f>I206/K206*1000</f>
+        <f t="shared" si="3"/>
         <v>20.408163265306122</v>
       </c>
       <c r="M206" s="1" t="s">
@@ -10690,7 +10703,7 @@
         <v>1.53</v>
       </c>
       <c r="L207" s="1">
-        <f>I207/K207*1000</f>
+        <f t="shared" si="3"/>
         <v>16.993464052287582</v>
       </c>
       <c r="M207" s="1" t="s">
@@ -10735,7 +10748,7 @@
         <v>5.22</v>
       </c>
       <c r="L208" s="1">
-        <f>I208/K208*1000</f>
+        <f t="shared" si="3"/>
         <v>41.187739463601531</v>
       </c>
       <c r="M208" s="1" t="s">
@@ -10780,7 +10793,7 @@
         <v>7.26</v>
       </c>
       <c r="L209" s="1">
-        <f>I209/K209*1000</f>
+        <f t="shared" si="3"/>
         <v>47.52066115702479</v>
       </c>
       <c r="M209" s="1" t="s">
@@ -10825,7 +10838,7 @@
         <v>2.81</v>
       </c>
       <c r="L210" s="1">
-        <f>I210/K210*1000</f>
+        <f t="shared" si="3"/>
         <v>60.4982206405694</v>
       </c>
       <c r="M210" s="1" t="s">
@@ -10870,7 +10883,7 @@
         <v>2.91</v>
       </c>
       <c r="L211" s="1">
-        <f>I211/K211*1000</f>
+        <f t="shared" si="3"/>
         <v>73.883161512027499</v>
       </c>
       <c r="M211" s="1" t="s">
@@ -10915,7 +10928,7 @@
         <v>1.56</v>
       </c>
       <c r="L212" s="1">
-        <f>I212/K212*1000</f>
+        <f t="shared" si="3"/>
         <v>32.051282051282058</v>
       </c>
       <c r="M212" s="1" t="s">
@@ -10960,7 +10973,7 @@
         <v>4.38</v>
       </c>
       <c r="L213" s="1">
-        <f>I213/K213*1000</f>
+        <f t="shared" si="3"/>
         <v>111.87214611872146</v>
       </c>
       <c r="M213" s="1" t="s">
@@ -11005,7 +11018,7 @@
         <v>4.5199999999999996</v>
       </c>
       <c r="L214" s="1">
-        <f>I214/K214*1000</f>
+        <f t="shared" si="3"/>
         <v>49.778761061946909</v>
       </c>
       <c r="M214" s="1" t="s">
@@ -11050,7 +11063,7 @@
         <v>3.01</v>
       </c>
       <c r="L215" s="1">
-        <f>I215/K215*1000</f>
+        <f t="shared" si="3"/>
         <v>74.750830564784053</v>
       </c>
       <c r="M215" s="1" t="s">
@@ -11095,7 +11108,7 @@
         <v>1.62</v>
       </c>
       <c r="L216" s="1">
-        <f>I216/K216*1000</f>
+        <f t="shared" si="3"/>
         <v>61.728395061728392</v>
       </c>
       <c r="M216" s="1" t="s">
@@ -11140,7 +11153,7 @@
         <v>2.8</v>
       </c>
       <c r="L217" s="1">
-        <f>I217/K217*1000</f>
+        <f t="shared" si="3"/>
         <v>101.78571428571429</v>
       </c>
       <c r="M217" s="1" t="s">
@@ -11185,7 +11198,7 @@
         <v>2.64</v>
       </c>
       <c r="L218" s="1">
-        <f>I218/K218*1000</f>
+        <f t="shared" si="3"/>
         <v>70.075757575757564</v>
       </c>
       <c r="M218" s="1" t="s">
@@ -11230,7 +11243,7 @@
         <v>2.74</v>
       </c>
       <c r="L219" s="1">
-        <f>I219/K219*1000</f>
+        <f t="shared" si="3"/>
         <v>32.846715328467148</v>
       </c>
       <c r="M219" s="1" t="s">
@@ -11275,7 +11288,7 @@
         <v>3.25</v>
       </c>
       <c r="L220" s="1">
-        <f>I220/K220*1000</f>
+        <f t="shared" si="3"/>
         <v>69.230769230769241</v>
       </c>
       <c r="M220" s="1" t="s">
@@ -11320,7 +11333,7 @@
         <v>3.85</v>
       </c>
       <c r="L221" s="1">
-        <f>I221/K221*1000</f>
+        <f t="shared" si="3"/>
         <v>116.88311688311688</v>
       </c>
       <c r="M221" s="1" t="s">
@@ -11365,7 +11378,7 @@
         <v>3.12</v>
       </c>
       <c r="L222" s="1">
-        <f>I222/K222*1000</f>
+        <f t="shared" si="3"/>
         <v>36.858974358974358</v>
       </c>
       <c r="M222" s="1" t="s">
@@ -11410,7 +11423,7 @@
         <v>3.13</v>
       </c>
       <c r="L223" s="1">
-        <f>I223/K223*1000</f>
+        <f t="shared" si="3"/>
         <v>103.83386581469649</v>
       </c>
       <c r="M223" s="1" t="s">
@@ -11455,7 +11468,7 @@
         <v>3.79</v>
       </c>
       <c r="L224" s="1">
-        <f>I224/K224*1000</f>
+        <f t="shared" si="3"/>
         <v>79.155672823218993</v>
       </c>
       <c r="M224" s="1" t="s">
@@ -11500,7 +11513,7 @@
         <v>2.38</v>
       </c>
       <c r="L225" s="1">
-        <f>I225/K225*1000</f>
+        <f t="shared" si="3"/>
         <v>65.12605042016807</v>
       </c>
       <c r="M225" s="1" t="s">
@@ -11545,7 +11558,7 @@
         <v>4.12</v>
       </c>
       <c r="L226" s="1">
-        <f>I226/K226*1000</f>
+        <f t="shared" si="3"/>
         <v>47.33009708737864</v>
       </c>
       <c r="M226" s="1" t="s">
@@ -11590,7 +11603,7 @@
         <v>1.55</v>
       </c>
       <c r="L227" s="1">
-        <f>I227/K227*1000</f>
+        <f t="shared" si="3"/>
         <v>41.935483870967744</v>
       </c>
       <c r="M227" s="1" t="s">
@@ -11635,7 +11648,7 @@
         <v>4.13</v>
       </c>
       <c r="L228" s="1">
-        <f>I228/K228*1000</f>
+        <f t="shared" si="3"/>
         <v>30.26634382566586</v>
       </c>
       <c r="M228" s="1" t="s">
@@ -11680,7 +11693,7 @@
         <v>3.27</v>
       </c>
       <c r="L229" s="1">
-        <f>I229/K229*1000</f>
+        <f t="shared" si="3"/>
         <v>116.20795107033639</v>
       </c>
       <c r="M229" s="1" t="s">
@@ -11725,7 +11738,7 @@
         <v>1.65</v>
       </c>
       <c r="L230" s="1">
-        <f>I230/K230*1000</f>
+        <f t="shared" si="3"/>
         <v>48.484848484848492</v>
       </c>
       <c r="M230" s="1" t="s">
@@ -11770,7 +11783,7 @@
         <v>4.0199999999999996</v>
       </c>
       <c r="L231" s="1">
-        <f>I231/K231*1000</f>
+        <f t="shared" si="3"/>
         <v>33.582089552238813</v>
       </c>
       <c r="M231" s="1" t="s">
@@ -11815,7 +11828,7 @@
         <v>2.64</v>
       </c>
       <c r="L232" s="1">
-        <f>I232/K232*1000</f>
+        <f t="shared" si="3"/>
         <v>75.757575757575765</v>
       </c>
       <c r="M232" s="1" t="s">
@@ -11860,7 +11873,7 @@
         <v>4.03</v>
       </c>
       <c r="L233" s="1">
-        <f>I233/K233*1000</f>
+        <f t="shared" si="3"/>
         <v>34.739454094292803</v>
       </c>
       <c r="M233" s="1" t="s">
@@ -11905,7 +11918,7 @@
         <v>4.45</v>
       </c>
       <c r="L234" s="1">
-        <f>I234/K234*1000</f>
+        <f t="shared" si="3"/>
         <v>82.022471910112358</v>
       </c>
       <c r="M234" s="1" t="s">
@@ -11950,7 +11963,7 @@
         <v>2.25</v>
       </c>
       <c r="L235" s="1">
-        <f>I235/K235*1000</f>
+        <f t="shared" si="3"/>
         <v>88.888888888888886</v>
       </c>
       <c r="M235" s="1" t="s">
@@ -11995,7 +12008,7 @@
         <v>2.16</v>
       </c>
       <c r="L236" s="1">
-        <f>I236/K236*1000</f>
+        <f t="shared" si="3"/>
         <v>32.407407407407405</v>
       </c>
       <c r="M236" s="1" t="s">
@@ -12040,7 +12053,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="L237" s="1">
-        <f>I237/K237*1000</f>
+        <f t="shared" si="3"/>
         <v>15.90909090909091</v>
       </c>
       <c r="M237" s="1" t="s">
@@ -12085,7 +12098,7 @@
         <v>3.16</v>
       </c>
       <c r="L238" s="1">
-        <f>I238/K238*1000</f>
+        <f t="shared" si="3"/>
         <v>31.645569620253166</v>
       </c>
       <c r="M238" s="1" t="s">
@@ -12130,7 +12143,7 @@
         <v>3.51</v>
       </c>
       <c r="L239" s="1">
-        <f>I239/K239*1000</f>
+        <f t="shared" si="3"/>
         <v>29.914529914529915</v>
       </c>
       <c r="M239" s="1" t="s">
@@ -12175,7 +12188,7 @@
         <v>2.87</v>
       </c>
       <c r="L240" s="1">
-        <f>I240/K240*1000</f>
+        <f t="shared" si="3"/>
         <v>22.648083623693381</v>
       </c>
       <c r="M240" s="1" t="s">
@@ -12220,7 +12233,7 @@
         <v>2.06</v>
       </c>
       <c r="L241" s="1">
-        <f>I241/K241*1000</f>
+        <f t="shared" si="3"/>
         <v>53.398058252427184</v>
       </c>
       <c r="M241" s="1" t="s">
@@ -12265,7 +12278,7 @@
         <v>1.46</v>
       </c>
       <c r="L242" s="1">
-        <f>I242/K242*1000</f>
+        <f t="shared" si="3"/>
         <v>136.98630136986304</v>
       </c>
       <c r="M242" s="1" t="s">
@@ -12310,7 +12323,7 @@
         <v>1.19</v>
       </c>
       <c r="L243" s="1">
-        <f>I243/K243*1000</f>
+        <f t="shared" si="3"/>
         <v>147.05882352941177</v>
       </c>
       <c r="M243" s="1" t="s">
@@ -12355,7 +12368,7 @@
         <v>2.21</v>
       </c>
       <c r="L244" s="1">
-        <f>I244/K244*1000</f>
+        <f t="shared" si="3"/>
         <v>119.90950226244344</v>
       </c>
       <c r="M244" s="1" t="s">
@@ -12400,7 +12413,7 @@
         <v>5.35</v>
       </c>
       <c r="L245" s="1">
-        <f>I245/K245*1000</f>
+        <f t="shared" si="3"/>
         <v>38.317757009345797</v>
       </c>
       <c r="M245" s="1" t="s">
@@ -12445,7 +12458,7 @@
         <v>3.09</v>
       </c>
       <c r="L246" s="1">
-        <f>I246/K246*1000</f>
+        <f t="shared" si="3"/>
         <v>48.543689320388346</v>
       </c>
       <c r="M246" s="1" t="s">
@@ -12490,7 +12503,7 @@
         <v>3.96</v>
       </c>
       <c r="L247" s="1">
-        <f>I247/K247*1000</f>
+        <f t="shared" si="3"/>
         <v>29.040404040404045</v>
       </c>
       <c r="M247" s="1" t="s">
@@ -12535,7 +12548,7 @@
         <v>3.73</v>
       </c>
       <c r="L248" s="1">
-        <f>I248/K248*1000</f>
+        <f t="shared" si="3"/>
         <v>60.321715817694368</v>
       </c>
       <c r="M248" s="1" t="s">
@@ -12580,7 +12593,7 @@
         <v>4.4800000000000004</v>
       </c>
       <c r="L249" s="1">
-        <f>I249/K249*1000</f>
+        <f t="shared" si="3"/>
         <v>30.133928571428573</v>
       </c>
       <c r="M249" s="1" t="s">
@@ -12625,7 +12638,7 @@
         <v>3</v>
       </c>
       <c r="L250" s="1">
-        <f>I250/K250*1000</f>
+        <f t="shared" si="3"/>
         <v>60</v>
       </c>
       <c r="M250" s="1" t="s">
@@ -12670,7 +12683,7 @@
         <v>3.09</v>
       </c>
       <c r="L251" s="1">
-        <f>I251/K251*1000</f>
+        <f t="shared" si="3"/>
         <v>33.980582524271846</v>
       </c>
       <c r="M251" s="1" t="s">
@@ -12715,7 +12728,7 @@
         <v>4.78</v>
       </c>
       <c r="L252" s="1">
-        <f>I252/K252*1000</f>
+        <f t="shared" si="3"/>
         <v>26.15062761506276</v>
       </c>
       <c r="M252" s="1" t="s">
@@ -12760,7 +12773,7 @@
         <v>1.82</v>
       </c>
       <c r="L253" s="1">
-        <f>I253/K253*1000</f>
+        <f t="shared" si="3"/>
         <v>68.681318681318672</v>
       </c>
       <c r="M253" s="1" t="s">
@@ -12805,7 +12818,7 @@
         <v>3.05</v>
       </c>
       <c r="L254" s="1">
-        <f>I254/K254*1000</f>
+        <f t="shared" si="3"/>
         <v>26.229508196721316</v>
       </c>
       <c r="M254" s="1" t="s">
@@ -12850,7 +12863,7 @@
         <v>4.1100000000000003</v>
       </c>
       <c r="L255" s="1">
-        <f>I255/K255*1000</f>
+        <f t="shared" si="3"/>
         <v>57.177615571776151</v>
       </c>
       <c r="M255" s="1" t="s">
@@ -12895,7 +12908,7 @@
         <v>3.7</v>
       </c>
       <c r="L256" s="1">
-        <f>I256/K256*1000</f>
+        <f t="shared" si="3"/>
         <v>58.108108108108105</v>
       </c>
       <c r="M256" s="1" t="s">
@@ -12940,7 +12953,7 @@
         <v>2.06</v>
       </c>
       <c r="L257" s="1">
-        <f>I257/K257*1000</f>
+        <f t="shared" si="3"/>
         <v>80.097087378640779</v>
       </c>
       <c r="M257" s="1" t="s">
@@ -12985,7 +12998,7 @@
         <v>2.31</v>
       </c>
       <c r="L258" s="1">
-        <f>I258/K258*1000</f>
+        <f t="shared" ref="L258:L300" si="4">I258/K258*1000</f>
         <v>145.02164502164501</v>
       </c>
       <c r="M258" s="1" t="s">
@@ -13030,7 +13043,7 @@
         <v>2.42</v>
       </c>
       <c r="L259" s="1">
-        <f>I259/K259*1000</f>
+        <f t="shared" si="4"/>
         <v>10.330578512396695</v>
       </c>
       <c r="M259" s="1" t="s">
@@ -13075,7 +13088,7 @@
         <v>2.56</v>
       </c>
       <c r="L260" s="1">
-        <f>I260/K260*1000</f>
+        <f t="shared" si="4"/>
         <v>58.59375</v>
       </c>
       <c r="M260" s="1" t="s">
@@ -13120,7 +13133,7 @@
         <v>2.83</v>
       </c>
       <c r="L261" s="1">
-        <f>I261/K261*1000</f>
+        <f t="shared" si="4"/>
         <v>24.734982332155479</v>
       </c>
       <c r="M261" s="1" t="s">
@@ -13165,7 +13178,7 @@
         <v>2.81</v>
       </c>
       <c r="L262" s="1">
-        <f>I262/K262*1000</f>
+        <f t="shared" si="4"/>
         <v>90.747330960854086</v>
       </c>
       <c r="M262" s="1" t="s">
@@ -13210,7 +13223,7 @@
         <v>4.1900000000000004</v>
       </c>
       <c r="L263" s="1">
-        <f>I263/K263*1000</f>
+        <f t="shared" si="4"/>
         <v>50.119331742243432</v>
       </c>
       <c r="M263" s="1" t="s">
@@ -13255,7 +13268,7 @@
         <v>2.88</v>
       </c>
       <c r="L264" s="1">
-        <f>I264/K264*1000</f>
+        <f t="shared" si="4"/>
         <v>88.541666666666671</v>
       </c>
       <c r="M264" s="1" t="s">
@@ -13300,7 +13313,7 @@
         <v>1.9</v>
       </c>
       <c r="L265" s="1">
-        <f>I265/K265*1000</f>
+        <f t="shared" si="4"/>
         <v>81.578947368421055</v>
       </c>
       <c r="M265" s="1" t="s">
@@ -13345,7 +13358,7 @@
         <v>2.2799999999999998</v>
       </c>
       <c r="L266" s="1">
-        <f>I266/K266*1000</f>
+        <f t="shared" si="4"/>
         <v>48.245614035087726</v>
       </c>
       <c r="M266" s="1" t="s">
@@ -13390,7 +13403,7 @@
         <v>2.91</v>
       </c>
       <c r="L267" s="1">
-        <f>I267/K267*1000</f>
+        <f t="shared" si="4"/>
         <v>41.237113402061858</v>
       </c>
       <c r="M267" s="1" t="s">
@@ -13435,7 +13448,7 @@
         <v>3</v>
       </c>
       <c r="L268" s="1">
-        <f>I268/K268*1000</f>
+        <f t="shared" si="4"/>
         <v>21.666666666666668</v>
       </c>
       <c r="M268" s="1" t="s">
@@ -13480,7 +13493,7 @@
         <v>1.37</v>
       </c>
       <c r="L269" s="1">
-        <f>I269/K269*1000</f>
+        <f t="shared" si="4"/>
         <v>36.496350364963497</v>
       </c>
       <c r="M269" s="1" t="s">
@@ -13525,7 +13538,7 @@
         <v>1.69</v>
       </c>
       <c r="L270" s="1">
-        <f>I270/K270*1000</f>
+        <f t="shared" si="4"/>
         <v>91.715976331360949</v>
       </c>
       <c r="M270" s="1" t="s">
@@ -13570,7 +13583,7 @@
         <v>3.13</v>
       </c>
       <c r="L271" s="1">
-        <f>I271/K271*1000</f>
+        <f t="shared" si="4"/>
         <v>75.079872204472849</v>
       </c>
       <c r="M271" s="1" t="s">
@@ -13615,7 +13628,7 @@
         <v>3.15</v>
       </c>
       <c r="L272" s="1">
-        <f>I272/K272*1000</f>
+        <f t="shared" si="4"/>
         <v>22.222222222222225</v>
       </c>
       <c r="M272" s="1" t="s">
@@ -13660,7 +13673,7 @@
         <v>3.28</v>
       </c>
       <c r="L273" s="1">
-        <f>I273/K273*1000</f>
+        <f t="shared" si="4"/>
         <v>32.012195121951223</v>
       </c>
       <c r="M273" s="1" t="s">
@@ -13705,7 +13718,7 @@
         <v>2.0099999999999998</v>
       </c>
       <c r="L274" s="1">
-        <f>I274/K274*1000</f>
+        <f t="shared" si="4"/>
         <v>104.47761194029852</v>
       </c>
       <c r="M274" s="1" t="s">
@@ -13750,7 +13763,7 @@
         <v>2.1800000000000002</v>
       </c>
       <c r="L275" s="1">
-        <f>I275/K275*1000</f>
+        <f t="shared" si="4"/>
         <v>64.22018348623854</v>
       </c>
       <c r="M275" s="1" t="s">
@@ -13795,7 +13808,7 @@
         <v>2.48</v>
       </c>
       <c r="L276" s="1">
-        <f>I276/K276*1000</f>
+        <f t="shared" si="4"/>
         <v>64.516129032258064</v>
       </c>
       <c r="M276" s="1" t="s">
@@ -13840,7 +13853,7 @@
         <v>5.97</v>
       </c>
       <c r="L277" s="1">
-        <f>I277/K277*1000</f>
+        <f t="shared" si="4"/>
         <v>42.713567839195981</v>
       </c>
       <c r="M277" s="1" t="s">
@@ -13885,7 +13898,7 @@
         <v>1.19</v>
       </c>
       <c r="L278" s="1">
-        <f>I278/K278*1000</f>
+        <f t="shared" si="4"/>
         <v>117.64705882352942</v>
       </c>
       <c r="M278" s="1" t="s">
@@ -13930,7 +13943,7 @@
         <v>3.33</v>
       </c>
       <c r="L279" s="1">
-        <f>I279/K279*1000</f>
+        <f t="shared" si="4"/>
         <v>60.06006006006006</v>
       </c>
       <c r="M279" s="1" t="s">
@@ -13975,7 +13988,7 @@
         <v>3.32</v>
       </c>
       <c r="L280" s="1">
-        <f>I280/K280*1000</f>
+        <f t="shared" si="4"/>
         <v>96.385542168674704</v>
       </c>
       <c r="M280" s="1" t="s">
@@ -14020,7 +14033,7 @@
         <v>1.93</v>
       </c>
       <c r="L281" s="1">
-        <f>I281/K281*1000</f>
+        <f t="shared" si="4"/>
         <v>101.03626943005183</v>
       </c>
       <c r="M281" s="1" t="s">
@@ -14065,7 +14078,7 @@
         <v>2.25</v>
       </c>
       <c r="L282" s="1">
-        <f>I282/K282*1000</f>
+        <f t="shared" si="4"/>
         <v>28.888888888888889</v>
       </c>
       <c r="M282" s="1" t="s">
@@ -14110,7 +14123,7 @@
         <v>1.77</v>
       </c>
       <c r="L283" s="1">
-        <f>I283/K283*1000</f>
+        <f t="shared" si="4"/>
         <v>45.197740112994353</v>
       </c>
       <c r="M283" s="1" t="s">
@@ -14155,7 +14168,7 @@
         <v>2.39</v>
       </c>
       <c r="L284" s="1">
-        <f>I284/K284*1000</f>
+        <f t="shared" si="4"/>
         <v>50.209205020920493</v>
       </c>
       <c r="M284" s="1" t="s">
@@ -14200,7 +14213,7 @@
         <v>2.94</v>
       </c>
       <c r="L285" s="1">
-        <f>I285/K285*1000</f>
+        <f t="shared" si="4"/>
         <v>57.823129251700685</v>
       </c>
       <c r="M285" s="1" t="s">
@@ -14245,7 +14258,7 @@
         <v>3.46</v>
       </c>
       <c r="L286" s="1">
-        <f>I286/K286*1000</f>
+        <f t="shared" si="4"/>
         <v>14.450867052023122</v>
       </c>
       <c r="M286" s="1" t="s">
@@ -14290,7 +14303,7 @@
         <v>2.86</v>
       </c>
       <c r="L287" s="1">
-        <f>I287/K287*1000</f>
+        <f t="shared" si="4"/>
         <v>64.685314685314694</v>
       </c>
       <c r="M287" s="1" t="s">
@@ -14335,7 +14348,7 @@
         <v>3.01</v>
       </c>
       <c r="L288" s="1">
-        <f>I288/K288*1000</f>
+        <f t="shared" si="4"/>
         <v>93.023255813953497</v>
       </c>
       <c r="M288" s="1" t="s">
@@ -14380,7 +14393,7 @@
         <v>3.28</v>
       </c>
       <c r="L289" s="1">
-        <f>I289/K289*1000</f>
+        <f t="shared" si="4"/>
         <v>62.5</v>
       </c>
       <c r="M289" s="1" t="s">
@@ -14425,7 +14438,7 @@
         <v>2.23</v>
       </c>
       <c r="L290" s="1">
-        <f>I290/K290*1000</f>
+        <f t="shared" si="4"/>
         <v>29.147982062780269</v>
       </c>
       <c r="M290" s="1" t="s">
@@ -14470,7 +14483,7 @@
         <v>2.9</v>
       </c>
       <c r="L291" s="1">
-        <f>I291/K291*1000</f>
+        <f t="shared" si="4"/>
         <v>15.517241379310345</v>
       </c>
       <c r="M291" s="1" t="s">
@@ -14515,7 +14528,7 @@
         <v>2.66</v>
       </c>
       <c r="L292" s="1">
-        <f>I292/K292*1000</f>
+        <f t="shared" si="4"/>
         <v>16.917293233082706</v>
       </c>
       <c r="M292" s="1" t="s">
@@ -14560,7 +14573,7 @@
         <v>1.62</v>
       </c>
       <c r="L293" s="1">
-        <f>I293/K293*1000</f>
+        <f t="shared" si="4"/>
         <v>52.469135802469133</v>
       </c>
       <c r="M293" s="1" t="s">
@@ -14605,7 +14618,7 @@
         <v>2.14</v>
       </c>
       <c r="L294" s="1">
-        <f>I294/K294*1000</f>
+        <f t="shared" si="4"/>
         <v>35.046728971962615</v>
       </c>
       <c r="M294" s="1" t="s">
@@ -14650,7 +14663,7 @@
         <v>2.1</v>
       </c>
       <c r="L295" s="1">
-        <f>I295/K295*1000</f>
+        <f t="shared" si="4"/>
         <v>61.904761904761905</v>
       </c>
       <c r="M295" s="1" t="s">
@@ -14695,7 +14708,7 @@
         <v>2.68</v>
       </c>
       <c r="L296" s="1">
-        <f>I296/K296*1000</f>
+        <f t="shared" si="4"/>
         <v>41.044776119402982</v>
       </c>
       <c r="M296" s="1" t="s">
@@ -14740,7 +14753,7 @@
         <v>2.58</v>
       </c>
       <c r="L297" s="1">
-        <f>I297/K297*1000</f>
+        <f t="shared" si="4"/>
         <v>36.821705426356587</v>
       </c>
       <c r="M297" s="1" t="s">
@@ -14785,7 +14798,7 @@
         <v>2.77</v>
       </c>
       <c r="L298" s="1">
-        <f>I298/K298*1000</f>
+        <f t="shared" si="4"/>
         <v>27.075812274368232</v>
       </c>
       <c r="M298" s="1" t="s">
@@ -14830,7 +14843,7 @@
         <v>3.81</v>
       </c>
       <c r="L299" s="1">
-        <f>I299/K299*1000</f>
+        <f t="shared" si="4"/>
         <v>30.183727034120736</v>
       </c>
       <c r="M299" s="1" t="s">
@@ -14875,7 +14888,7 @@
         <v>3.58</v>
       </c>
       <c r="L300" s="1">
-        <f>I300/K300*1000</f>
+        <f t="shared" si="4"/>
         <v>57.262569832402228</v>
       </c>
       <c r="M300" s="1" t="s">
@@ -14894,4 +14907,10 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{45011977-b912-4387-97a4-f4c94a801377}" enabled="1" method="Standard" siteId="{11d0e217-264e-400a-8ba0-57dcc127d72d}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>